--- a/IWAI-2026-assignments.xlsx
+++ b/IWAI-2026-assignments.xlsx
@@ -89,7 +89,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -125,12 +125,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,7 +176,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -211,11 +205,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -320,7 +310,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="1"/>
@@ -335,7 +325,7 @@
       <c r="A4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="1"/>
@@ -352,7 +342,7 @@
       <c r="A5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="1"/>
@@ -361,7 +351,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
     </row>
